--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05744838714599609</v>
+        <v>0.0571441650390625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8632988425449154</v>
+        <v>0.9572001745398507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9025974025974026</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8757306007306007</v>
+        <v>0.9604258947324641</v>
       </c>
       <c r="H2" t="n">
-        <v>0.991398212177433</v>
+        <v>0.999339405183561</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0549767017364502</v>
+        <v>0.05239343643188477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.872392295342498</v>
+        <v>0.9643310564221558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9025974025974026</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8757306007306007</v>
+        <v>0.9604258947324641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.991398212177433</v>
+        <v>0.999339405183561</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05744838714599609</v>
+        <v>0.0571441650390625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8632988425449154</v>
+        <v>0.9572001745398507</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9025974025974026</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8757306007306007</v>
+        <v>0.9604258947324641</v>
       </c>
       <c r="H2" t="n">
-        <v>0.991398212177433</v>
+        <v>0.999339405183561</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0549767017364502</v>
+        <v>0.05239343643188477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.872392295342498</v>
+        <v>0.9643310564221558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9025974025974026</v>
+        <v>0.9675324675324676</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8757306007306007</v>
+        <v>0.9604258947324641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.991398212177433</v>
+        <v>0.999339405183561</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0571441650390625</v>
+        <v>0.03340435028076172</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9572001745398507</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9675324675324676</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9604258947324641</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.999339405183561</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05239343643188477</v>
+        <v>0.03034567832946777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9643310564221558</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9675324675324676</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9604258947324641</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.999339405183561</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0571441650390625</v>
+        <v>0.03340435028076172</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9572001745398507</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9675324675324676</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9604258947324641</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.999339405183561</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05239343643188477</v>
+        <v>0.03034567832946777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9643310564221558</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9675324675324676</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9604258947324641</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.999339405183561</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03340435028076172</v>
+        <v>0.05903887748718262</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8045967478693122</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8027210884353742</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7126446579025013</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9669813503632745</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,21 +526,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03034567832946777</v>
+        <v>0.06962823867797852</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.7717468937346105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8027210884353742</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7126446579025013</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9669813503632745</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08653879165649414</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7836203875777444</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8027210884353742</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7126446579025013</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9669813503632745</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03340435028076172</v>
+        <v>0.05903887748718262</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8045967478693122</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8027210884353742</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7126446579025013</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9669813503632745</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,21 +692,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03034567832946777</v>
+        <v>0.06962823867797852</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.7717468937346105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8027210884353742</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7126446579025013</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9669813503632745</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08653879165649414</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7836203875777444</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8027210884353742</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7126446579025013</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9669813503632745</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05903887748718262</v>
+        <v>23.9944543838501</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8045967478693122</v>
+        <v>0.8260553486408432</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8027210884353742</v>
+        <v>0.8682393555811277</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7126446579025013</v>
+        <v>0.8355376548696518</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9669813503632745</v>
+        <v>0.9440887166702797</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06962823867797852</v>
+        <v>28.06601738929749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7717468937346105</v>
+        <v>0.8301691337493897</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8027210884353742</v>
+        <v>0.8682393555811277</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7126446579025013</v>
+        <v>0.8355376548696518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9669813503632745</v>
+        <v>0.9440887166702797</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -561,19 +561,19 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08653879165649414</v>
+        <v>39.27588891983032</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7836203875777444</v>
+        <v>0.8343505263916757</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8027210884353742</v>
+        <v>0.8682393555811277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7126446579025013</v>
+        <v>0.8355376548696518</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9669813503632745</v>
+        <v>0.9440887166702797</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05903887748718262</v>
+        <v>23.9944543838501</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8045967478693122</v>
+        <v>0.8260553486408432</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8027210884353742</v>
+        <v>0.8682393555811277</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7126446579025013</v>
+        <v>0.8355376548696518</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9669813503632745</v>
+        <v>0.9440887166702797</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,19 +692,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06962823867797852</v>
+        <v>28.06601738929749</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7717468937346105</v>
+        <v>0.8301691337493897</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8027210884353742</v>
+        <v>0.8682393555811277</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7126446579025013</v>
+        <v>0.8355376548696518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9669813503632745</v>
+        <v>0.9440887166702797</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08653879165649414</v>
+        <v>39.27588891983032</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7836203875777444</v>
+        <v>0.8343505263916757</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8027210884353742</v>
+        <v>0.8682393555811277</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7126446579025013</v>
+        <v>0.8355376548696518</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9669813503632745</v>
+        <v>0.9440887166702797</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.9944543838501</v>
+        <v>0.03442811965942383</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8260553486408432</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8355376548696518</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9440887166702797</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>28.06601738929749</v>
+        <v>0.0317833423614502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8301691337493897</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8355376548696518</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9440887166702797</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>39.27588891983032</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8343505263916757</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8682393555811277</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8355376548696518</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9440887166702797</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>23.9944543838501</v>
+        <v>0.03442811965942383</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8260553486408432</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8355376548696518</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9440887166702797</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>28.06601738929749</v>
+        <v>0.0317833423614502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8301691337493897</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8682393555811277</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8355376548696518</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9440887166702797</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>39.27588891983032</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8343505263916757</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8682393555811277</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8355376548696518</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9440887166702797</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03442811965942383</v>
+        <v>0.03517770767211914</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0317833423614502</v>
+        <v>0.03180122375488281</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03442811965942383</v>
+        <v>0.03517770767211914</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0317833423614502</v>
+        <v>0.03180122375488281</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03517770767211914</v>
+        <v>0.03382015228271484</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03180122375488281</v>
+        <v>0.03372740745544434</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03517770767211914</v>
+        <v>0.03382015228271484</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03180122375488281</v>
+        <v>0.03372740745544434</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03382015228271484</v>
+        <v>0.06094837188720703</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03372740745544434</v>
+        <v>0.09186434745788574</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03382015228271484</v>
+        <v>0.06094837188720703</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03372740745544434</v>
+        <v>0.09186434745788574</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06094837188720703</v>
+        <v>327.696958065033</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8329028339735882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09186434745788574</v>
+        <v>851.5462410449982</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8406821430035827</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06094837188720703</v>
+        <v>327.696958065033</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8329028339735882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09186434745788574</v>
+        <v>851.5462410449982</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8406821430035827</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>327.696958065033</v>
+        <v>43.40839552879333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8329028339735882</v>
+        <v>0.3860689683845369</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.63125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.3728667653804837</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.908822265625</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>851.5462410449982</v>
+        <v>66.89026546478271</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8406821430035827</v>
+        <v>0.3926733492464133</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.6125</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.3556169700366032</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.910568359375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>327.696958065033</v>
+        <v>43.40839552879333</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8329028339735882</v>
+        <v>0.3860689683845369</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.63125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.3728667653804837</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.908822265625</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>851.5462410449982</v>
+        <v>66.89026546478271</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8406821430035827</v>
+        <v>0.3926733492464133</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.6125</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.3556169700366032</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.910568359375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -488,22 +488,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>43.40839552879333</v>
+        <v>20413.65140247345</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3860689683845369</v>
+        <v>0.7749083896227867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.63125</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3728667653804837</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H2" t="n">
-        <v>0.908822265625</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>66.89026546478271</v>
+        <v>25779.20336675644</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3926733492464133</v>
+        <v>0.7829275385741383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6125</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3556169700366032</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.910568359375</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -619,22 +619,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>43.40839552879333</v>
+        <v>20413.65140247345</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3860689683845369</v>
+        <v>0.7749083896227867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.63125</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3728667653804837</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H2" t="n">
-        <v>0.908822265625</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>66.89026546478271</v>
+        <v>25779.20336675644</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3926733492464133</v>
+        <v>0.7829275385741383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6125</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3556169700366032</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.910568359375</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20413.65140247345</v>
+        <v>0.06463313102722168</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7749083896227867</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>25779.20336675644</v>
+        <v>0.1030514240264893</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7829275385741383</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20413.65140247345</v>
+        <v>0.06463313102722168</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7749083896227867</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>25779.20336675644</v>
+        <v>0.1030514240264893</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7829275385741383</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06463313102722168</v>
+        <v>0.05411744117736816</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1030514240264893</v>
+        <v>0.08301877975463867</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06463313102722168</v>
+        <v>0.05411744117736816</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1030514240264893</v>
+        <v>0.08301877975463867</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05411744117736816</v>
+        <v>0.1044347286224365</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08301877975463867</v>
+        <v>0.1007204055786133</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -543,6 +543,41 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1559367179870605</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967071524966261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05411744117736816</v>
+        <v>0.1044347286224365</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -657,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08301877975463867</v>
+        <v>0.1007204055786133</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -674,6 +709,41 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1559367179870605</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967071524966261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1044347286224365</v>
+        <v>0.0983879566192627</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1007204055786133</v>
+        <v>0.1738967895507812</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1559367179870605</v>
+        <v>0.2396857738494873</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967071524966261</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1044347286224365</v>
+        <v>0.0983879566192627</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1007204055786133</v>
+        <v>0.1738967895507812</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1559367179870605</v>
+        <v>0.2396857738494873</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967071524966261</v>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0983879566192627</v>
+        <v>0.08736753463745117</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1738967895507812</v>
+        <v>0.1757090091705322</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2396857738494873</v>
+        <v>0.2211108207702637</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967071524966261</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0983879566192627</v>
+        <v>0.08736753463745117</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1738967895507812</v>
+        <v>0.1757090091705322</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2396857738494873</v>
+        <v>0.2211108207702637</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967071524966261</v>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08736753463745117</v>
+        <v>220.4221472740173</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8329028339735882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -526,56 +526,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1757090091705322</v>
+        <v>404.337406873703</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8406821430035827</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2211108207702637</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967071524966261</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08736753463745117</v>
+        <v>220.4221472740173</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8329028339735882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -692,56 +657,21 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1757090091705322</v>
+        <v>404.337406873703</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8406821430035827</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8918296892980437</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8471046922758727</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9350138196401473</v>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.2211108207702637</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967071524966261</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>220.4221472740173</v>
+        <v>136.1728026866913</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8329028339735882</v>
+        <v>0.9996759964597205</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.9998444870665077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.9998444843919962</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.9999999892512356</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>404.337406873703</v>
+        <v>314.9365310668945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8406821430035827</v>
+        <v>0.9996759945997233</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.9998444870665077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.9998444843919962</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.9999999892512355</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>220.4221472740173</v>
+        <v>136.1728026866913</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8329028339735882</v>
+        <v>0.9996759964597205</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.9998444870665077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.9998444843919962</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.9999999892512356</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': None, 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>404.337406873703</v>
+        <v>314.9365310668945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8406821430035827</v>
+        <v>0.9996759945997233</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8918296892980437</v>
+        <v>0.9998444870665077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8471046922758727</v>
+        <v>0.9998444843919962</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9350138196401473</v>
+        <v>0.9999999892512355</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>136.1728026866913</v>
+        <v>167.733238697052</v>
       </c>
       <c r="E2" t="n">
         <v>0.9996759964597205</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>314.9365310668945</v>
+        <v>331.5528485774994</v>
       </c>
       <c r="E3" t="n">
         <v>0.9996759945997233</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>136.1728026866913</v>
+        <v>167.733238697052</v>
       </c>
       <c r="E2" t="n">
         <v>0.9996759964597205</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>314.9365310668945</v>
+        <v>331.5528485774994</v>
       </c>
       <c r="E3" t="n">
         <v>0.9996759945997233</v>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>167.733238697052</v>
+        <v>7582.797722101212</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9996759964597205</v>
+        <v>0.7749083896227867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998444870665077</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9998444843919962</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999892512356</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': None, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>331.5528485774994</v>
+        <v>13063.4157834053</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9996759945997233</v>
+        <v>0.7829275385741383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998444870665077</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9998444843919962</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999999892512355</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>167.733238697052</v>
+        <v>7582.797722101212</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9996759964597205</v>
+        <v>0.7749083896227867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998444870665077</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9998444843919962</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999892512356</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': None, 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>331.5528485774994</v>
+        <v>13063.4157834053</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9996759945997233</v>
+        <v>0.7829275385741383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998444870665077</v>
+        <v>0.9229794780846212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9998444843919962</v>
+        <v>0.7861985403124643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9999999892512355</v>
+        <v>0.9221847571388855</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7582.797722101212</v>
+        <v>351.8641495704651</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7749083896227867</v>
+        <v>0.9284502465999035</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9419233482247825</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9324042859331567</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9788942174844476</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13063.4157834053</v>
+        <v>761.6525349617004</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7829275385741383</v>
+        <v>0.9328469405523752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9454502703973665</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9369826450254473</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9795603357067736</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7582.797722101212</v>
+        <v>351.8641495704651</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7749083896227867</v>
+        <v>0.9284502465999035</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9419233482247825</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9324042859331567</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9788942174844476</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>13063.4157834053</v>
+        <v>761.6525349617004</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7829275385741383</v>
+        <v>0.9328469405523752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9229794780846212</v>
+        <v>0.9454502703973665</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7861985403124643</v>
+        <v>0.9369826450254473</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9221847571388855</v>
+        <v>0.9795603357067736</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>351.8641495704651</v>
+        <v>636.6349778175354</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9284502465999035</v>
+        <v>0.339159554098232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9419233482247825</v>
+        <v>0.6244897959183674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9324042859331567</v>
+        <v>0.3801460934017369</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9788942174844476</v>
+        <v>0.9203715465778147</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 100, 'class_weight': None, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>761.6525349617004</v>
+        <v>1314.020700931549</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9328469405523752</v>
+        <v>0.3495388752192812</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9454502703973665</v>
+        <v>0.6163265306122448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9369826450254473</v>
+        <v>0.3868945733264785</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9795603357067736</v>
+        <v>0.9204642162987644</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>351.8641495704651</v>
+        <v>636.6349778175354</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9284502465999035</v>
+        <v>0.339159554098232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9419233482247825</v>
+        <v>0.6244897959183674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9324042859331567</v>
+        <v>0.3801460934017369</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9788942174844476</v>
+        <v>0.9203715465778147</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'C': 100, 'class_weight': None, 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>761.6525349617004</v>
+        <v>1314.020700931549</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9328469405523752</v>
+        <v>0.3495388752192812</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9454502703973665</v>
+        <v>0.6163265306122448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9369826450254473</v>
+        <v>0.3868945733264785</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9795603357067736</v>
+        <v>0.9204642162987644</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 0.1, 'kernel': 'rbf'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>636.6349778175354</v>
+        <v>0.07866811752319336</v>
       </c>
       <c r="E2" t="n">
-        <v>0.339159554098232</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6244897959183674</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3801460934017369</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9203715465778147</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'gamma': 0.1, 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1314.020700931549</v>
+        <v>0.1310718059539795</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3495388752192812</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6163265306122448</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3868945733264785</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9204642162987644</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 0.1, 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2439649105072021</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967071524966261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>636.6349778175354</v>
+        <v>0.07866811752319336</v>
       </c>
       <c r="E2" t="n">
-        <v>0.339159554098232</v>
+        <v>0.9967294558426634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6244897959183674</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3801460934017369</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9203715465778147</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': None, 'gamma': 0.1, 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1314.020700931549</v>
+        <v>0.1310718059539795</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3495388752192812</v>
+        <v>0.9967253463310086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6163265306122448</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3868945733264785</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9204642162987644</v>
+        <v>0.9888513513513514</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'C': 100, 'class_weight': 'balanced', 'gamma': 0.1, 'kernel': 'rbf'}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2439649105072021</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9967071524966261</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07866811752319336</v>
+        <v>0.1257679462432861</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1310718059539795</v>
+        <v>0.1733777523040771</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2439649105072021</v>
+        <v>0.3622910976409912</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967071524966261</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07866811752319336</v>
+        <v>0.1257679462432861</v>
       </c>
       <c r="E2" t="n">
         <v>0.9967294558426634</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1310718059539795</v>
+        <v>0.1733777523040771</v>
       </c>
       <c r="E3" t="n">
         <v>0.9967253463310086</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2439649105072021</v>
+        <v>0.3622910976409912</v>
       </c>
       <c r="E4" t="n">
         <v>0.9967071524966261</v>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,22 +488,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1257679462432861</v>
+        <v>778.4893350601196</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8729324256296929</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8793918918918919</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8707109028397426</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9522532575048592</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1733777523040771</v>
+        <v>1741.498635292053</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8727232928382499</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.879054054054054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8701280874728412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.952378988393764</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3622910976409912</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967071524966261</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,22 +619,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1257679462432861</v>
+        <v>778.4893350601196</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9967294558426634</v>
+        <v>0.8729324256296929</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8793918918918919</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8707109028397426</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.9522532575048592</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1733777523040771</v>
+        <v>1741.498635292053</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9967253463310086</v>
+        <v>0.8727232928382499</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.879054054054054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8701280874728412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9888513513513514</v>
+        <v>0.952378988393764</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3622910976409912</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9967071524966261</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': None, 'C': 10}</t>
+          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>778.4893350601196</v>
+        <v>217.581684589386</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8729324256296929</v>
+        <v>0.9996620109119062</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8793918918918919</v>
+        <v>0.9999436746648642</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8707109028397426</v>
+        <v>0.9999436745145818</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9522532575048592</v>
+        <v>0.9999999365489514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1741.498635292053</v>
+        <v>405.432281255722</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8727232928382499</v>
+        <v>0.9997183417435679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.879054054054054</v>
+        <v>0.9999436746648642</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8701280874728412</v>
+        <v>0.9999436745145818</v>
       </c>
       <c r="H3" t="n">
-        <v>0.952378988393764</v>
+        <v>0.9999999365489514</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>778.4893350601196</v>
+        <v>217.581684589386</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8729324256296929</v>
+        <v>0.9996620109119062</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8793918918918919</v>
+        <v>0.9999436746648642</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8707109028397426</v>
+        <v>0.9999436745145818</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9522532575048592</v>
+        <v>0.9999999365489514</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1741.498635292053</v>
+        <v>405.432281255722</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8727232928382499</v>
+        <v>0.9997183417435679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.879054054054054</v>
+        <v>0.9999436746648642</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8701280874728412</v>
+        <v>0.9999436745145818</v>
       </c>
       <c r="H3" t="n">
-        <v>0.952378988393764</v>
+        <v>0.9999999365489514</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
+          <t>{'kernel': 'linear', 'gamma': 0.1, 'class_weight': 'balanced', 'C': 100}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_SVC_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>217.581684589386</v>
+        <v>158.3006844520569</v>
       </c>
       <c r="E2" t="n">
         <v>0.9996620109119062</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>405.432281255722</v>
+        <v>335.9704122543335</v>
       </c>
       <c r="E3" t="n">
         <v>0.9997183417435679</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>217.581684589386</v>
+        <v>158.3006844520569</v>
       </c>
       <c r="E2" t="n">
         <v>0.9996620109119062</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>405.432281255722</v>
+        <v>335.9704122543335</v>
       </c>
       <c r="E3" t="n">
         <v>0.9997183417435679</v>
